--- a/NỘI DUNG YÊU CẦU/Yêu cầu báo cáo 05-07-2025.xlsx
+++ b/NỘI DUNG YÊU CẦU/Yêu cầu báo cáo 05-07-2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 01-07-2025)\QUANLY-IT-Cai-Tien-Update-PM-\NỘI DUNG YÊU CẦU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 04-07-2025)\QUANLY-IT-Cai-Tien-Update-PM-\NỘI DUNG YÊU CẦU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3946B6EB-17ED-4608-887C-D3953F8B321B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE7DAF9-5894-4B46-8082-3947FD62511E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="35">
   <si>
     <t>Số lượng Office:</t>
   </si>
@@ -132,16 +132,33 @@
   </si>
   <si>
     <t>Try Test</t>
+  </si>
+  <si>
+    <t>Tại sao số lượng Office lại ít vậy thôi á</t>
+  </si>
+  <si>
+    <t>Lấy nhanh số seri ko mai họ nghỉ</t>
+  </si>
+  <si>
+    <t>Một trăm mười mấy Key Office.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -164,13 +181,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -190,16 +210,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>514351</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38101</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>447676</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>86378</xdr:rowOff>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>153053</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -222,8 +242,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="514351" y="552450"/>
-          <a:ext cx="10363200" cy="4677428"/>
+          <a:off x="647701" y="428625"/>
+          <a:ext cx="10410824" cy="4677428"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -498,18 +518,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="T1:AB31"/>
+  <dimension ref="B1:AB31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
     <col min="17" max="17" width="9.5703125" customWidth="1"/>
     <col min="18" max="18" width="9.7109375" customWidth="1"/>
     <col min="19" max="19" width="8.42578125" customWidth="1"/>
-    <col min="20" max="20" width="15.5703125" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" customWidth="1"/>
     <col min="21" max="21" width="11.5703125" customWidth="1"/>
     <col min="22" max="22" width="10.85546875" customWidth="1"/>
-    <col min="24" max="24" width="10.28515625" customWidth="1"/>
-    <col min="25" max="25" width="11.85546875" customWidth="1"/>
+    <col min="24" max="24" width="11.28515625" customWidth="1"/>
+    <col min="25" max="25" width="10.85546875" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="20:25" x14ac:dyDescent="0.25">
@@ -518,7 +539,7 @@
       </c>
     </row>
     <row r="2" spans="20:25" x14ac:dyDescent="0.25">
-      <c r="T2" t="s">
+      <c r="T2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -543,6 +564,16 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9" spans="20:25" x14ac:dyDescent="0.25">
+      <c r="Y9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="20:25" x14ac:dyDescent="0.25">
+      <c r="Y10" t="s">
+        <v>32</v>
+      </c>
+    </row>
     <row r="11" spans="20:25" x14ac:dyDescent="0.25">
       <c r="Y11" t="s">
         <v>7</v>
@@ -552,8 +583,11 @@
       <c r="T15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="17" spans="20:28" x14ac:dyDescent="0.25">
+      <c r="X15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="T17" t="s">
         <v>9</v>
       </c>
@@ -564,7 +598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U18" t="s">
         <v>11</v>
       </c>
@@ -572,7 +606,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U19" t="s">
         <v>12</v>
       </c>
@@ -580,7 +614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U20" t="s">
         <v>13</v>
       </c>
@@ -588,7 +622,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U21" t="s">
         <v>14</v>
       </c>
@@ -596,7 +630,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
       <c r="Y23" t="s">
         <v>20</v>
       </c>
@@ -607,7 +641,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
       <c r="T24" t="s">
         <v>17</v>
       </c>
@@ -630,7 +664,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U25" t="s">
         <v>28</v>
       </c>
@@ -644,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U26" t="s">
         <v>18</v>
       </c>
@@ -658,7 +692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U27" t="s">
         <v>29</v>
       </c>
@@ -666,7 +700,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U28" t="s">
         <v>19</v>
       </c>
@@ -674,7 +708,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
       <c r="U29" t="s">
         <v>30</v>
       </c>
@@ -682,18 +719,21 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="U30" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="20:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
       <c r="X31" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="T2" r:id="rId1" xr:uid="{CEDEA109-0A36-46C9-942A-883F93827C62}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/NỘI DUNG YÊU CẦU/Yêu cầu báo cáo 05-07-2025.xlsx
+++ b/NỘI DUNG YÊU CẦU/Yêu cầu báo cáo 05-07-2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 04-07-2025)\QUANLY-IT-Cai-Tien-Update-PM-\NỘI DUNG YÊU CẦU\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 19-10-2025)\QUANLY-IT-Cai-Tien-Update-PM-\NỘI DUNG YÊU CẦU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AE7DAF9-5894-4B46-8082-3947FD62511E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2581FF8-7861-43BC-B1E0-BB4FA1CCF5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,16 +210,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>38101</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>31953</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>153053</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>134003</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -242,8 +242,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="647701" y="428625"/>
-          <a:ext cx="10410824" cy="4677428"/>
+          <a:off x="1251153" y="85725"/>
+          <a:ext cx="10283622" cy="4620278"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
